--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99049</v>
+        <v>99050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99050</v>
+        <v>99051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99051</v>
+        <v>99054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99054</v>
+        <v>99055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99055</v>
+        <v>99057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108189</v>
       </c>
       <c r="B2" t="n">
-        <v>99062</v>
+        <v>99063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131108189</v>
+        <v>123701628</v>
       </c>
       <c r="B2" t="n">
-        <v>99063</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,24 +708,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öst Hermansberget, Mpd</t>
+          <t>Tjäder, Nora, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598912</v>
+        <v>598790</v>
       </c>
       <c r="R2" t="n">
-        <v>6931306</v>
+        <v>6931250</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +750,19 @@
           <t>Sättna</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2025-0658</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tjäder som blev ivägskrämd när jag kom gåendes.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,15 +777,257 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131108189</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Öst Hermansberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>598912</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6931306</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2025-0658</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131106523</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Öst Hermansberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598877</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6931413</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2025_0657</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Forsberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 51586-2025 artfynd.xlsx
+++ b/artfynd/A 51586-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108189</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,8 +1047,18 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>